--- a/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>sortOrder</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>recycleScrap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +554,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,6 +624,11 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>排序(物资面板与图鉴)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>回收站分解一件得到的废料(FG4-ECO-02;只有固体&gt;0;少于做它花掉的废料当量,FG16 FGR-BAL-050)</t>
         </is>
       </c>
     </row>
@@ -673,6 +688,9 @@
       <c r="M4" t="n">
         <v>10</v>
       </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -730,6 +748,9 @@
       <c r="M5" t="n">
         <v>20</v>
       </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -787,6 +808,9 @@
       <c r="M6" t="n">
         <v>30</v>
       </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -844,6 +868,9 @@
       <c r="M7" t="n">
         <v>40</v>
       </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -901,6 +928,9 @@
       <c r="M8" t="n">
         <v>50</v>
       </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -958,6 +988,9 @@
       <c r="M9" t="n">
         <v>60</v>
       </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1015,6 +1048,9 @@
       <c r="M10" t="n">
         <v>70</v>
       </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1072,6 +1108,9 @@
       <c r="M11" t="n">
         <v>80</v>
       </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1129,6 +1168,9 @@
       <c r="M12" t="n">
         <v>90</v>
       </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1186,6 +1228,9 @@
       <c r="M13" t="n">
         <v>100</v>
       </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1243,6 +1288,9 @@
       <c r="M14" t="n">
         <v>110</v>
       </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1300,6 +1348,9 @@
       <c r="M15" t="n">
         <v>120</v>
       </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1357,6 +1408,9 @@
       <c r="M16" t="n">
         <v>130</v>
       </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1414,6 +1468,9 @@
       <c r="M17" t="n">
         <v>140</v>
       </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1471,6 +1528,9 @@
       <c r="M18" t="n">
         <v>150</v>
       </c>
+      <c r="N18" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1528,6 +1588,9 @@
       <c r="M19" t="n">
         <v>160</v>
       </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1585,6 +1648,9 @@
       <c r="M20" t="n">
         <v>170</v>
       </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1642,6 +1708,9 @@
       <c r="M21" t="n">
         <v>180</v>
       </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1699,6 +1768,9 @@
       <c r="M22" t="n">
         <v>190</v>
       </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1756,6 +1828,9 @@
       <c r="M23" t="n">
         <v>200</v>
       </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1813,6 +1888,9 @@
       <c r="M24" t="n">
         <v>210</v>
       </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1870,6 +1948,9 @@
       <c r="M25" t="n">
         <v>220</v>
       </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1927,6 +2008,9 @@
       <c r="M26" t="n">
         <v>230</v>
       </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1984,6 +2068,9 @@
       <c r="M27" t="n">
         <v>300</v>
       </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2041,6 +2128,9 @@
       <c r="M28" t="n">
         <v>310</v>
       </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2098,6 +2188,9 @@
       <c r="M29" t="n">
         <v>320</v>
       </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2155,6 +2248,9 @@
       <c r="M30" t="n">
         <v>330</v>
       </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2212,6 +2308,9 @@
       <c r="M31" t="n">
         <v>340</v>
       </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2269,6 +2368,9 @@
       <c r="M32" t="n">
         <v>400</v>
       </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2325,6 +2427,9 @@
       </c>
       <c r="M33" t="n">
         <v>410</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,15 +1716,15 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>human_legacy</t>
+          <t>enemy_wreck</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vault</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1737,46 +1737,46 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>item.human_legacy.name</t>
+          <t>item.enemy_wreck.name</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>item.human_legacy.desc</t>
+          <t>item.enemy_wreck.desc</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>item.human_legacy.source</t>
+          <t>item.enemy_wreck.source</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>item.human_legacy.use</t>
+          <t>item.enemy_wreck.use</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>#FFD166</t>
+          <t>#6B5B4B</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>square</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>listening_array_core</t>
+          <t>human_legacy</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1797,36 +1797,36 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>item.listening_array_core.name</t>
+          <t>item.human_legacy.name</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>item.listening_array_core.desc</t>
+          <t>item.human_legacy.desc</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>item.listening_array_core.source</t>
+          <t>item.human_legacy.source</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>item.listening_array_core.use</t>
+          <t>item.human_legacy.use</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>#90BE6D</t>
+          <t>#FFD166</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>furnace_heart</t>
+          <t>listening_array_core</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1857,27 +1857,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>item.furnace_heart.name</t>
+          <t>item.listening_array_core.name</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>item.furnace_heart.desc</t>
+          <t>item.listening_array_core.desc</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>item.furnace_heart.source</t>
+          <t>item.listening_array_core.source</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>item.furnace_heart.use</t>
+          <t>item.listening_array_core.use</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>#F94144</t>
+          <t>#90BE6D</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>reactor_core</t>
+          <t>furnace_heart</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>item.reactor_core.name</t>
+          <t>item.furnace_heart.name</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>item.reactor_core.desc</t>
+          <t>item.furnace_heart.desc</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>item.reactor_core.source</t>
+          <t>item.furnace_heart.source</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>item.reactor_core.use</t>
+          <t>item.furnace_heart.use</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>#43AA8B</t>
+          <t>#F94144</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1956,7 +1956,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>supercomputer_core</t>
+          <t>reactor_core</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1977,27 +1977,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.name</t>
+          <t>item.reactor_core.name</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.desc</t>
+          <t>item.reactor_core.desc</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.source</t>
+          <t>item.reactor_core.source</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.use</t>
+          <t>item.reactor_core.use</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>#577590</t>
+          <t>#43AA8B</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>supercomputer_core</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2024,49 +2024,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>vault</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>key</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>item.water.name</t>
+          <t>item.supercomputer_core.name</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>item.water.desc</t>
+          <t>item.supercomputer_core.desc</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>item.water.source</t>
+          <t>item.supercomputer_core.source</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>item.water.use</t>
+          <t>item.supercomputer_core.use</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>#3C8DDC</t>
+          <t>#577590</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2093,31 +2093,31 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>item.crude.name</t>
+          <t>item.water.name</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>item.crude.desc</t>
+          <t>item.water.desc</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>item.crude.source</t>
+          <t>item.water.source</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>item.crude.use</t>
+          <t>item.water.use</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>#8A5A2E</t>
+          <t>#3C8DDC</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>coolant</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>item.coolant.name</t>
+          <t>item.crude.name</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>item.coolant.desc</t>
+          <t>item.crude.desc</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>item.coolant.source</t>
+          <t>item.crude.source</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>item.coolant.use</t>
+          <t>item.crude.use</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>#3FD0C0</t>
+          <t>#8A5A2E</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>coolant</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2213,31 +2213,31 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>item.fuel.name</t>
+          <t>item.coolant.name</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>item.fuel.desc</t>
+          <t>item.coolant.desc</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>item.fuel.source</t>
+          <t>item.coolant.source</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>item.fuel.use</t>
+          <t>item.coolant.use</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>#E8A33A</t>
+          <t>#3FD0C0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>acid</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2273,31 +2273,31 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>item.acid.name</t>
+          <t>item.fuel.name</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>item.acid.desc</t>
+          <t>item.fuel.desc</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>item.acid.source</t>
+          <t>item.fuel.source</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>item.acid.use</t>
+          <t>item.fuel.use</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>#A6D93A</t>
+          <t>#E8A33A</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>acid</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2324,49 +2324,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>item.tech_data.name</t>
+          <t>item.acid.name</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>item.tech_data.desc</t>
+          <t>item.acid.desc</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>item.tech_data.source</t>
+          <t>item.acid.source</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>item.tech_data.use</t>
+          <t>item.acid.use</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>#7FDBFF</t>
+          <t>#A6D93A</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>pill</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2376,59 +2376,119 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
+          <t>tech_data</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>item.tech_data.name</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>item.tech_data.desc</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>item.tech_data.source</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>item.tech_data.use</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>#7FDBFF</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>pill</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>400</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>research_points</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>item.research_points.name</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>item.research_points.desc</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>item.research_points.source</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>item.research_points.use</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>#B39DDB</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>pill</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>410</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,11 +1296,11 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>structure_module</t>
+          <t>drop_pod</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1317,54 +1317,54 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>item.structure_module.name</t>
+          <t>item.drop_pod.name</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>item.structure_module.desc</t>
+          <t>item.drop_pod.desc</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>item.structure_module.source</t>
+          <t>item.drop_pod.source</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>item.structure_module.use</t>
+          <t>item.drop_pod.use</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>#8D6A9F</t>
+          <t>#F2C14E</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>pill</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>firmware_chip</t>
+          <t>structure_module</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1377,46 +1377,46 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>item.firmware_chip.name</t>
+          <t>item.structure_module.name</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>item.firmware_chip.desc</t>
+          <t>item.structure_module.desc</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>item.firmware_chip.source</t>
+          <t>item.structure_module.source</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>item.firmware_chip.use</t>
+          <t>item.structure_module.use</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>#3D7DD8</t>
+          <t>#8D6A9F</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>firmware_chip</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1437,36 +1437,36 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>item.machine.name</t>
+          <t>item.firmware_chip.name</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>item.machine.desc</t>
+          <t>item.firmware_chip.desc</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>item.machine.source</t>
+          <t>item.firmware_chip.source</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>item.machine.use</t>
+          <t>item.firmware_chip.use</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>#F2F2F2</t>
+          <t>#3D7DD8</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>square</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1476,20 +1476,20 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>megastructure_part</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>solid</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>endgame</t>
+          <t>product</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1497,50 +1497,50 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>item.megastructure_part.name</t>
+          <t>item.machine.name</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>item.megastructure_part.desc</t>
+          <t>item.machine.desc</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>item.megastructure_part.source</t>
+          <t>item.machine.source</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>item.megastructure_part.use</t>
+          <t>item.machine.use</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>#F4A261</t>
+          <t>#F2F2F2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="N18" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>unparsed_module</t>
+          <t>megastructure_part</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>expedition</t>
+          <t>endgame</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1557,50 +1557,50 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>item.unparsed_module.name</t>
+          <t>item.megastructure_part.name</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>item.unparsed_module.desc</t>
+          <t>item.megastructure_part.desc</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>item.unparsed_module.source</t>
+          <t>item.megastructure_part.source</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>item.unparsed_module.use</t>
+          <t>item.megastructure_part.use</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>#A0A0A0</t>
+          <t>#F4A261</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>encrypted_firmware</t>
+          <t>unparsed_module</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1617,36 +1617,36 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>item.encrypted_firmware.name</t>
+          <t>item.unparsed_module.name</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>item.encrypted_firmware.desc</t>
+          <t>item.unparsed_module.desc</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>item.encrypted_firmware.source</t>
+          <t>item.unparsed_module.source</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>item.encrypted_firmware.use</t>
+          <t>item.unparsed_module.use</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>#5C6BC0</t>
+          <t>#A0A0A0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>pill</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1656,11 +1656,11 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data_core</t>
+          <t>encrypted_firmware</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1677,36 +1677,36 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>item.data_core.name</t>
+          <t>item.encrypted_firmware.name</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>item.data_core.desc</t>
+          <t>item.encrypted_firmware.desc</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>item.data_core.source</t>
+          <t>item.encrypted_firmware.source</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>item.data_core.use</t>
+          <t>item.encrypted_firmware.use</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>#26C6DA</t>
+          <t>#5C6BC0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>pill</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
@@ -1716,11 +1716,11 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>enemy_wreck</t>
+          <t>data_core</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1737,36 +1737,36 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>item.enemy_wreck.name</t>
+          <t>item.data_core.name</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>item.enemy_wreck.desc</t>
+          <t>item.data_core.desc</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>item.enemy_wreck.source</t>
+          <t>item.data_core.source</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>item.enemy_wreck.use</t>
+          <t>item.data_core.use</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>#6B5B4B</t>
+          <t>#26C6DA</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -1776,15 +1776,15 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>human_legacy</t>
+          <t>enemy_wreck</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>vault</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1797,46 +1797,46 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>item.human_legacy.name</t>
+          <t>item.enemy_wreck.name</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>item.human_legacy.desc</t>
+          <t>item.enemy_wreck.desc</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>item.human_legacy.source</t>
+          <t>item.enemy_wreck.source</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>item.human_legacy.use</t>
+          <t>item.enemy_wreck.use</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>#FFD166</t>
+          <t>#6B5B4B</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>square</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>listening_array_core</t>
+          <t>human_legacy</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>expedition</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1857,36 +1857,36 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>item.listening_array_core.name</t>
+          <t>item.human_legacy.name</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>item.listening_array_core.desc</t>
+          <t>item.human_legacy.desc</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>item.listening_array_core.source</t>
+          <t>item.human_legacy.source</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>item.listening_array_core.use</t>
+          <t>item.human_legacy.use</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>#90BE6D</t>
+          <t>#FFD166</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>furnace_heart</t>
+          <t>listening_array_core</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>item.furnace_heart.name</t>
+          <t>item.listening_array_core.name</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>item.furnace_heart.desc</t>
+          <t>item.listening_array_core.desc</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>item.furnace_heart.source</t>
+          <t>item.listening_array_core.source</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>item.furnace_heart.use</t>
+          <t>item.listening_array_core.use</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>#F94144</t>
+          <t>#90BE6D</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1956,7 +1956,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>reactor_core</t>
+          <t>furnace_heart</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1977,27 +1977,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>item.reactor_core.name</t>
+          <t>item.furnace_heart.name</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>item.reactor_core.desc</t>
+          <t>item.furnace_heart.desc</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>item.reactor_core.source</t>
+          <t>item.furnace_heart.source</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>item.reactor_core.use</t>
+          <t>item.furnace_heart.use</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>#43AA8B</t>
+          <t>#F94144</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>supercomputer_core</t>
+          <t>reactor_core</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.name</t>
+          <t>item.reactor_core.name</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.desc</t>
+          <t>item.reactor_core.desc</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.source</t>
+          <t>item.reactor_core.source</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>item.supercomputer_core.use</t>
+          <t>item.reactor_core.use</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>#577590</t>
+          <t>#43AA8B</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>supercomputer_core</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2084,49 +2084,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>vault</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>key</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>item.water.name</t>
+          <t>item.supercomputer_core.name</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>item.water.desc</t>
+          <t>item.supercomputer_core.desc</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>item.water.source</t>
+          <t>item.supercomputer_core.source</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>item.water.use</t>
+          <t>item.supercomputer_core.use</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>#3C8DDC</t>
+          <t>#577590</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>item.crude.name</t>
+          <t>item.water.name</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>item.crude.desc</t>
+          <t>item.water.desc</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>item.crude.source</t>
+          <t>item.water.source</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>item.crude.use</t>
+          <t>item.water.use</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>#8A5A2E</t>
+          <t>#3C8DDC</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>coolant</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2213,31 +2213,31 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>item.coolant.name</t>
+          <t>item.crude.name</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>item.coolant.desc</t>
+          <t>item.crude.desc</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>item.coolant.source</t>
+          <t>item.crude.source</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>item.coolant.use</t>
+          <t>item.crude.use</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>#3FD0C0</t>
+          <t>#8A5A2E</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>coolant</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2273,31 +2273,31 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>item.fuel.name</t>
+          <t>item.coolant.name</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>item.fuel.desc</t>
+          <t>item.coolant.desc</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>item.fuel.source</t>
+          <t>item.coolant.source</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>item.fuel.use</t>
+          <t>item.coolant.use</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>#E8A33A</t>
+          <t>#3FD0C0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>acid</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2333,31 +2333,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>item.acid.name</t>
+          <t>item.fuel.name</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>item.acid.desc</t>
+          <t>item.fuel.desc</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>item.acid.source</t>
+          <t>item.fuel.source</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>item.acid.use</t>
+          <t>item.fuel.use</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>#A6D93A</t>
+          <t>#E8A33A</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>tech_data</t>
+          <t>acid</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2384,49 +2384,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>item.tech_data.name</t>
+          <t>item.acid.name</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>item.tech_data.desc</t>
+          <t>item.acid.desc</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>item.tech_data.source</t>
+          <t>item.acid.source</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>item.tech_data.use</t>
+          <t>item.acid.use</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>#7FDBFF</t>
+          <t>#A6D93A</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>pill</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2436,59 +2436,119 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
+          <t>tech_data</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>item.tech_data.name</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>item.tech_data.desc</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>item.tech_data.source</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>item.tech_data.use</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>#7FDBFF</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>pill</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>400</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>research_points</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>digital</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>item.research_points.name</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>item.research_points.desc</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>item.research_points.source</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>item.research_points.use</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>#B39DDB</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>pill</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>410</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EcoItem-物品.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>recycleScrap</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +564,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +639,11 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>回收站分解一件得到的废料(FG4-ECO-02;只有固体&gt;0;少于做它花掉的废料当量,FG16 FGR-BAL-050)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>协议(FG8-LOOT-01 FGR-LOOT-001):own己方/neutral中立=直接使用;enemy敌方加密=必须送解析台(敌方固件破解前可由信号核裸跑)</t>
         </is>
       </c>
     </row>
@@ -691,6 +706,11 @@
       <c r="N4" t="n">
         <v>1</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -751,6 +771,11 @@
       <c r="N5" t="n">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -811,6 +836,11 @@
       <c r="N6" t="n">
         <v>1</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -871,6 +901,11 @@
       <c r="N7" t="n">
         <v>2</v>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -931,6 +966,11 @@
       <c r="N8" t="n">
         <v>1</v>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -991,6 +1031,11 @@
       <c r="N9" t="n">
         <v>4</v>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1051,6 +1096,11 @@
       <c r="N10" t="n">
         <v>2</v>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1111,6 +1161,11 @@
       <c r="N11" t="n">
         <v>4</v>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1171,6 +1226,11 @@
       <c r="N12" t="n">
         <v>5</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1231,6 +1291,11 @@
       <c r="N13" t="n">
         <v>2</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1291,6 +1356,11 @@
       <c r="N14" t="n">
         <v>4</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1351,6 +1421,11 @@
       <c r="N15" t="n">
         <v>21</v>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1411,6 +1486,11 @@
       <c r="N16" t="n">
         <v>9</v>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1471,6 +1551,11 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1531,6 +1616,11 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1591,6 +1681,11 @@
       <c r="N19" t="n">
         <v>39</v>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1651,6 +1746,11 @@
       <c r="N20" t="n">
         <v>1</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1711,6 +1811,11 @@
       <c r="N21" t="n">
         <v>1</v>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1771,6 +1876,11 @@
       <c r="N22" t="n">
         <v>1</v>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1831,6 +1941,11 @@
       <c r="N23" t="n">
         <v>1</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1891,6 +2006,11 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1951,6 +2071,11 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -2011,6 +2136,11 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2071,6 +2201,11 @@
       <c r="N27" t="n">
         <v>0</v>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2131,6 +2266,11 @@
       <c r="N28" t="n">
         <v>0</v>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2191,6 +2331,11 @@
       <c r="N29" t="n">
         <v>0</v>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2251,6 +2396,11 @@
       <c r="N30" t="n">
         <v>0</v>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2311,6 +2461,11 @@
       <c r="N31" t="n">
         <v>0</v>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2371,6 +2526,11 @@
       <c r="N32" t="n">
         <v>0</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2431,6 +2591,11 @@
       <c r="N33" t="n">
         <v>0</v>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2491,6 +2656,11 @@
       <c r="N34" t="n">
         <v>0</v>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2550,6 +2720,11 @@
       </c>
       <c r="N35" t="n">
         <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
       </c>
     </row>
   </sheetData>
